--- a/Monthly warehouse expenses.xlsx
+++ b/Monthly warehouse expenses.xlsx
@@ -8,18 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karishma.das\Documents\CJ DARCL\Operations\Monthly Opex Expenses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1808712E-BED1-47D0-B111-0D53C7DE33A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6145AC09-020F-47BF-991D-246E0D8AAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD753405-8938-40ED-BF9C-A6CE89EB6A85}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-27" sheetId="1" r:id="rId1"/>
     <sheet name="Budget" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-27'!$A$2:$U$234</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -128,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="115">
   <si>
     <t>FY</t>
   </si>
@@ -472,31 +470,7 @@
     <t>Snacks for visitor</t>
   </si>
   <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>LIFELONG</t>
-  </si>
-  <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>Friday</t>
-  </si>
-  <si>
-    <t>Monday</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
   </si>
 </sst>
 </file>
@@ -945,7 +919,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1618,34 +1592,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12281,7 +12227,7 @@
         <v>46235</v>
       </c>
       <c r="C174" s="137" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D174" s="137" t="s">
         <v>64</v>
@@ -15648,495 +15594,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D718B2AB-DDE1-49C6-88C2-B2C4352EE8CC}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="27.90625" style="231" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" style="231" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="231"/>
-    <col min="4" max="4" width="11.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="229" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="238" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="238" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="237" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="237" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="234"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="230" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="230" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="236">
-        <v>46324</v>
-      </c>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="230" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="230" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="230" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="230" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="234"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="230" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="230" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="230" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="230" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="234"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="230" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="230" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="234"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="230" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="230" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="234"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="230" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="234"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="230" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="234"/>
-      <c r="E10" s="232"/>
-      <c r="F10" s="232"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="230" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="230" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="234"/>
-      <c r="E11" s="232"/>
-      <c r="F11" s="232"/>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="230" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="230" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="230" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="230" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="230" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="230" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="230" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="230" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="230" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="230" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="230" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="230" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="230" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="230" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="230" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="230" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="230" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="230" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="230" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="230" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="230" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="230" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="230" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="230" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="206" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="235">
-        <v>46321</v>
-      </c>
-      <c r="E21" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="234"/>
-    </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="230" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="206" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="235">
-        <v>46321</v>
-      </c>
-      <c r="E22" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="F22" s="234"/>
-    </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="230" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="206" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="235">
-        <v>46321</v>
-      </c>
-      <c r="E23" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="F23" s="234"/>
-    </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="230" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="206" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="235">
-        <v>46321</v>
-      </c>
-      <c r="E24" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="234"/>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="230" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="206" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="232"/>
-      <c r="E25" s="232"/>
-      <c r="F25" s="234"/>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="230" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="206" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="232"/>
-      <c r="E26" s="232"/>
-      <c r="F26" s="234"/>
-    </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="230" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="206" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="235">
-        <v>46322</v>
-      </c>
-      <c r="E27" s="234" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="234"/>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="230" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="206" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="235">
-        <v>46322</v>
-      </c>
-      <c r="E28" s="234" t="s">
-        <v>122</v>
-      </c>
-      <c r="F28" s="234"/>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="230" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="206" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="235">
-        <v>46322</v>
-      </c>
-      <c r="E29" s="234" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="234"/>
-    </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="230" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="230" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="230" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="233">
-        <v>46317</v>
-      </c>
-      <c r="E30" s="232" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="232"/>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="230" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="230" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="230" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="235">
-        <v>46318</v>
-      </c>
-      <c r="E31" s="232" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="232"/>
-    </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="230" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="230" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="230" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="235">
-        <v>46318</v>
-      </c>
-      <c r="E32" s="232" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="232"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E32" xr:uid="{D718B2AB-DDE1-49C6-88C2-B2C4352EE8CC}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="WEST"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Monthly warehouse expenses.xlsx
+++ b/Monthly warehouse expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karishma.das\Documents\CJ DARCL\Operations\Monthly Opex Expenses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6145AC09-020F-47BF-991D-246E0D8AAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920D81F4-8BFA-4071-BC2D-EF7D81F499C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD753405-8938-40ED-BF9C-A6CE89EB6A85}"/>
   </bookViews>
@@ -437,9 +437,6 @@
     <t>DASNA-3</t>
   </si>
   <si>
-    <t>VAS</t>
-  </si>
-  <si>
     <t>VI-JOHN</t>
   </si>
   <si>
@@ -471,6 +468,9 @@
   </si>
   <si>
     <t>LIFELONG</t>
+  </si>
+  <si>
+    <t>VAS MP</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2046,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>8</v>
@@ -2355,7 +2355,7 @@
         <v>46113</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>22</v>
@@ -9857,7 +9857,7 @@
         <v>8500</v>
       </c>
       <c r="T131" s="178" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U131" s="16">
         <f t="shared" si="2"/>
@@ -10362,7 +10362,7 @@
         <v>13272</v>
       </c>
       <c r="T141" s="73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U141" s="16">
         <f t="shared" si="3"/>
@@ -10472,7 +10472,7 @@
         <v>34608</v>
       </c>
       <c r="T143" s="73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U143" s="16">
         <f t="shared" si="3"/>
@@ -12227,7 +12227,7 @@
         <v>46235</v>
       </c>
       <c r="C174" s="137" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D174" s="137" t="s">
         <v>64</v>
@@ -12564,7 +12564,7 @@
         <v>36433</v>
       </c>
       <c r="T180" s="153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U180" s="16">
         <f t="shared" si="5"/>
@@ -12827,10 +12827,10 @@
         <v>46235</v>
       </c>
       <c r="C186" s="137" t="s">
+        <v>104</v>
+      </c>
+      <c r="D186" s="137" t="s">
         <v>105</v>
-      </c>
-      <c r="D186" s="137" t="s">
-        <v>106</v>
       </c>
       <c r="E186" s="137" t="s">
         <v>23</v>
@@ -13118,7 +13118,7 @@
         <v>46235</v>
       </c>
       <c r="C191" s="137" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D191" s="137" t="s">
         <v>36</v>
@@ -13278,7 +13278,7 @@
         <v>137763</v>
       </c>
       <c r="T193" s="159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="U193" s="16">
         <f t="shared" si="5"/>
@@ -14429,7 +14429,7 @@
         <v>36733</v>
       </c>
       <c r="T218" s="209" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U218" s="16">
         <f t="shared" si="6"/>
@@ -14553,7 +14553,7 @@
         <v>45923</v>
       </c>
       <c r="T221" s="213" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U221" s="16">
         <f t="shared" si="6"/>
@@ -14650,10 +14650,10 @@
         <v>46266</v>
       </c>
       <c r="C224" s="189" t="s">
+        <v>104</v>
+      </c>
+      <c r="D224" s="189" t="s">
         <v>105</v>
-      </c>
-      <c r="D224" s="189" t="s">
-        <v>106</v>
       </c>
       <c r="E224" s="189" t="s">
         <v>23</v>
@@ -14887,7 +14887,7 @@
         <v>46266</v>
       </c>
       <c r="C229" s="189" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D229" s="189" t="s">
         <v>36</v>
